--- a/data/gravel/Manzanita Whippet 2025.xlsx
+++ b/data/gravel/Manzanita Whippet 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8876CE8B-9DEE-5C42-8D6B-1DAB41C62C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3101DA-F020-1447-A5C0-60119D1DC84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2480" yWindow="500" windowWidth="25280" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -414,6 +414,9 @@
   </si>
   <si>
     <t>a8:j39</t>
+  </si>
+  <si>
+    <t>https://manzanitacycles.com/assets/img/whippet-main-1800w.avif</t>
   </si>
 </sst>
 </file>
@@ -981,6 +984,9 @@
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="C6" s="1">
         <v>74.900000000000006</v>
       </c>
@@ -2045,31 +2051,31 @@
         <v>160</v>
       </c>
       <c r="D36" s="9">
-        <f>AVERAGE(C41:D41)</f>
+        <f t="shared" ref="D36:J36" si="1">AVERAGE(C41:D41)</f>
         <v>163.74389051808407</v>
       </c>
       <c r="E36" s="9">
-        <f>AVERAGE(D41:E41)</f>
+        <f t="shared" si="1"/>
         <v>168.97360703812313</v>
       </c>
       <c r="F36" s="9">
-        <f>AVERAGE(E41:F41)</f>
+        <f t="shared" si="1"/>
         <v>174.07624633431084</v>
       </c>
       <c r="G36" s="9">
-        <f>AVERAGE(F41:G41)</f>
+        <f t="shared" si="1"/>
         <v>178.92473118279568</v>
       </c>
       <c r="H36" s="9">
-        <f>AVERAGE(G41:H41)</f>
+        <f t="shared" si="1"/>
         <v>184.10557184750735</v>
       </c>
       <c r="I36" s="9">
-        <f>AVERAGE(H41:I41)</f>
+        <f t="shared" si="1"/>
         <v>189.71652003910071</v>
       </c>
       <c r="J36" s="9">
-        <f>AVERAGE(I41:J41)</f>
+        <f t="shared" si="1"/>
         <v>194.97230368198112</v>
       </c>
       <c r="K36" s="1" t="s">
@@ -2085,27 +2091,27 @@
         <v>163.74389051808407</v>
       </c>
       <c r="D37" s="9">
-        <f>AVERAGE(D41:E41)</f>
+        <f t="shared" ref="D37:I37" si="2">AVERAGE(D41:E41)</f>
         <v>168.97360703812313</v>
       </c>
       <c r="E37" s="9">
-        <f>AVERAGE(E41:F41)</f>
+        <f t="shared" si="2"/>
         <v>174.07624633431084</v>
       </c>
       <c r="F37" s="9">
-        <f>AVERAGE(F41:G41)</f>
+        <f t="shared" si="2"/>
         <v>178.92473118279568</v>
       </c>
       <c r="G37" s="9">
-        <f>AVERAGE(G41:H41)</f>
+        <f t="shared" si="2"/>
         <v>184.10557184750735</v>
       </c>
       <c r="H37" s="9">
-        <f>AVERAGE(H41:I41)</f>
+        <f t="shared" si="2"/>
         <v>189.71652003910071</v>
       </c>
       <c r="I37" s="9">
-        <f>AVERAGE(I41:J41)</f>
+        <f t="shared" si="2"/>
         <v>194.97230368198112</v>
       </c>
       <c r="J37" s="9">
@@ -2134,31 +2140,31 @@
         <v>161.07526881720432</v>
       </c>
       <c r="D41" s="10">
-        <f t="shared" ref="D41:J41" si="1">D42/0.465</f>
+        <f t="shared" ref="D41:J41" si="3">D42/0.465</f>
         <v>166.4125122189638</v>
       </c>
       <c r="E41" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>171.5347018572825</v>
       </c>
       <c r="F41" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>176.61779081133918</v>
       </c>
       <c r="G41" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>181.23167155425219</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>186.97947214076248</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>192.45356793743892</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>197.49103942652332</v>
       </c>
       <c r="K41" s="1" t="s">
@@ -2177,31 +2183,31 @@
         <v>74.900000000000006</v>
       </c>
       <c r="D42" s="9">
-        <f t="shared" ref="D42:J42" si="2">(D$10-D$1)/(D$2-D$1) * (D6 - D5) + D5</f>
+        <f t="shared" ref="D42:J42" si="4">(D$10-D$1)/(D$2-D$1) * (D6 - D5) + D5</f>
         <v>77.381818181818176</v>
       </c>
       <c r="E42" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>79.763636363636365</v>
       </c>
       <c r="F42" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>82.127272727272725</v>
       </c>
       <c r="G42" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>84.272727272727266</v>
       </c>
       <c r="H42" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>86.945454545454552</v>
       </c>
       <c r="I42" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>89.490909090909099</v>
       </c>
       <c r="J42" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>91.833333333333343</v>
       </c>
       <c r="K42" s="6" t="s">

--- a/data/gravel/Manzanita Whippet 2025.xlsx
+++ b/data/gravel/Manzanita Whippet 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3101DA-F020-1447-A5C0-60119D1DC84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC9DCA3-3CC1-5243-A679-7F572E924596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2480" yWindow="500" windowWidth="25280" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="130">
   <si>
     <t>brand</t>
   </si>
@@ -353,9 +353,6 @@
     <t>steel</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>external</t>
   </si>
   <si>
@@ -417,6 +414,15 @@
   </si>
   <si>
     <t>https://manzanitacycles.com/assets/img/whippet-main-1800w.avif</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Reno, Nevada, USA</t>
   </si>
 </sst>
 </file>
@@ -800,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:S80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -840,7 +846,7 @@
         <v>807</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -875,7 +881,7 @@
         <v>819</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -910,7 +916,7 @@
         <v>59.4</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -945,7 +951,7 @@
         <v>60.3</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -980,12 +986,12 @@
         <v>91.4</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" s="1">
         <v>74.900000000000006</v>
@@ -1012,7 +1018,7 @@
         <v>92.7</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -1020,7 +1026,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -1028,7 +1034,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>80</v>
@@ -1057,10 +1063,10 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C9" s="9">
         <f>(C$10-C$1)/(C$2-C$1) * (C4 - C3) + C3</f>
@@ -1095,7 +1101,7 @@
         <v>59.699999999999996</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1107,7 +1113,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>88</v>
@@ -1476,7 +1482,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>97</v>
@@ -1517,7 +1523,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>98</v>
@@ -1711,7 +1717,7 @@
         <v>53</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
@@ -1727,7 +1733,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C25" s="7">
         <v>410</v>
@@ -2079,7 +2085,7 @@
         <v>194.97230368198112</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
@@ -2168,7 +2174,7 @@
         <v>197.49103942652332</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
@@ -2211,7 +2217,7 @@
         <v>91.833333333333343</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
@@ -2368,7 +2374,7 @@
         <v>51</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -2462,7 +2468,15 @@
         <v>65</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>106</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Manzanita Whippet 2025.xlsx
+++ b/data/gravel/Manzanita Whippet 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC9DCA3-3CC1-5243-A679-7F572E924596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1FDD78-C51E-4649-8C81-5889A93F1576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2480" yWindow="500" windowWidth="25280" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="136">
   <si>
     <t>brand</t>
   </si>
@@ -423,6 +423,24 @@
   </si>
   <si>
     <t>Reno, Nevada, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -806,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S80"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -2311,171 +2329,201 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="1">
-        <v>27.2</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B60" s="1">
-        <v>42</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B62" s="1">
-        <v>180</v>
+        <v>42</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B63" s="1">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B64" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>72</v>
+        <v>46</v>
+      </c>
+      <c r="B66" s="1">
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B68" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B69" s="1">
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B72" s="1">
-        <v>3</v>
+        <v>52</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76" s="1">
-        <v>2600</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="1">
-        <v>4850</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
+      </c>
+      <c r="B78" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B82" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B83" s="1">
+        <v>4850</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>129</v>
       </c>
     </row>
